--- a/StructureDefinition-openimis-insurance-plan.xlsx
+++ b/StructureDefinition-openimis-insurance-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -11346,7 +11346,7 @@
         <v>77</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>22</v>
@@ -11994,7 +11994,7 @@
         <v>77</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>22</v>
@@ -12100,7 +12100,7 @@
         <v>77</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>22</v>
@@ -12312,7 +12312,7 @@
         <v>77</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>22</v>
@@ -12422,7 +12422,7 @@
         <v>77</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>22</v>
@@ -12530,7 +12530,7 @@
         <v>77</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>22</v>
@@ -13172,7 +13172,7 @@
         <v>77</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>22</v>
@@ -13814,7 +13814,7 @@
         <v>77</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>22</v>
@@ -20188,7 +20188,7 @@
         <v>77</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>22</v>
@@ -20294,7 +20294,7 @@
         <v>77</v>
       </c>
       <c r="G162" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H162" t="s" s="2">
         <v>22</v>
@@ -20400,7 +20400,7 @@
         <v>77</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>22</v>
@@ -20506,7 +20506,7 @@
         <v>77</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H164" t="s" s="2">
         <v>22</v>
@@ -21358,7 +21358,7 @@
         <v>77</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>22</v>
@@ -23404,7 +23404,7 @@
         <v>77</v>
       </c>
       <c r="G191" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H191" t="s" s="2">
         <v>22</v>
@@ -25238,7 +25238,7 @@
         <v>77</v>
       </c>
       <c r="G208" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H208" t="s" s="2">
         <v>22</v>
@@ -25450,7 +25450,7 @@
         <v>77</v>
       </c>
       <c r="G210" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H210" t="s" s="2">
         <v>22</v>
@@ -27284,7 +27284,7 @@
         <v>77</v>
       </c>
       <c r="G227" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H227" t="s" s="2">
         <v>22</v>
@@ -27496,7 +27496,7 @@
         <v>77</v>
       </c>
       <c r="G229" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H229" t="s" s="2">
         <v>22</v>
@@ -29330,7 +29330,7 @@
         <v>77</v>
       </c>
       <c r="G246" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H246" t="s" s="2">
         <v>22</v>
@@ -29542,7 +29542,7 @@
         <v>77</v>
       </c>
       <c r="G248" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H248" t="s" s="2">
         <v>22</v>
@@ -31376,7 +31376,7 @@
         <v>77</v>
       </c>
       <c r="G265" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H265" t="s" s="2">
         <v>22</v>
@@ -31588,7 +31588,7 @@
         <v>77</v>
       </c>
       <c r="G267" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H267" t="s" s="2">
         <v>22</v>
@@ -33422,7 +33422,7 @@
         <v>77</v>
       </c>
       <c r="G284" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H284" t="s" s="2">
         <v>22</v>
@@ -33634,7 +33634,7 @@
         <v>77</v>
       </c>
       <c r="G286" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H286" t="s" s="2">
         <v>22</v>
@@ -35468,7 +35468,7 @@
         <v>77</v>
       </c>
       <c r="G303" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H303" t="s" s="2">
         <v>22</v>
@@ -35680,7 +35680,7 @@
         <v>77</v>
       </c>
       <c r="G305" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H305" t="s" s="2">
         <v>22</v>
@@ -35786,7 +35786,7 @@
         <v>77</v>
       </c>
       <c r="G306" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H306" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-insurance-plan.xlsx
+++ b/StructureDefinition-openimis-insurance-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-insurance-plan.xlsx
+++ b/StructureDefinition-openimis-insurance-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
